--- a/results/block3_results/segment stenosis/Normal_1/stenosis_summary_Normal_1.xlsx
+++ b/results/block3_results/segment stenosis/Normal_1/stenosis_summary_Normal_1.xlsx
@@ -477,11 +477,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>First diagonal (D1)</t>
+          <t>LCX posterolateral branch</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,11 +491,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LCX</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>91.80868804884203</v>
+        <v>93.27278844286676</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="I2" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>90.35137770105396</v>
+        <v>92.69234155339068</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -546,30 +546,30 @@
         <v>233</v>
       </c>
       <c r="I3" t="n">
-        <v>200</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LCX posterolateral branch</t>
+          <t>Right PDA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LCX</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>88.00096534996815</v>
+        <v>86.1559559717453</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -580,33 +580,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="I4" t="n">
-        <v>134</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Right PDA</t>
+          <t>Mid LAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>86.84242426320652</v>
+        <v>85.50953385499778</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -617,33 +617,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="I5" t="n">
-        <v>224</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mid LAD</t>
+          <t>Unmapped segment 19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>Unmapped</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>Unmapped</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>84.71822983802619</v>
+        <v>83.54090399876489</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -654,33 +654,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>206</v>
+        <v>373</v>
       </c>
       <c r="I6" t="n">
-        <v>191</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unmapped segment 19</t>
+          <t>Distal LCX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unmapped</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Unmapped</t>
+          <t>LCX</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>82.73888446055896</v>
+        <v>79.90736409423839</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="I7" t="n">
-        <v>300</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79.10915580861952</v>
+        <v>77.8576911786642</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -731,16 +731,16 @@
         <v>776</v>
       </c>
       <c r="I8" t="n">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Distal LCX</t>
+          <t>Distal LAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -750,34 +750,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LCX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>78.66652148198055</v>
+        <v>65.61645780401632</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
+          <t>Moderate stenosis</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="I9" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Left Main</t>
+          <t>First obtuse marginal (OM1)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -787,85 +787,85 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>LCX</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.49159409819676</v>
+        <v>65.51280273104059</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
+          <t>Moderate stenosis</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>363</v>
+        <v>635</v>
       </c>
       <c r="I10" t="n">
-        <v>160</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>First obtuse marginal (OM1)</t>
+          <t>Distal RCA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LCX</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71.02875962329487</v>
+        <v>64.31046045191174</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
+          <t>Moderate stenosis</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>635</v>
+        <v>925</v>
       </c>
       <c r="I11" t="n">
-        <v>594</v>
+        <v>925</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Distal RCA</t>
+          <t>Proximal LCX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCX</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>63.76964624909517</v>
+        <v>50.13626362211434</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -876,19 +876,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>925</v>
+        <v>268</v>
       </c>
       <c r="I12" t="n">
-        <v>925</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Distal LAD</t>
+          <t>Left coronary PDA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -898,173 +898,165 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LCX</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>57.17407343198862</v>
+        <v>45.79088806727626</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moderate stenosis</t>
+          <t>Mild stenosis</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>235</v>
+        <v>804</v>
       </c>
       <c r="I13" t="n">
-        <v>228</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Proximal LCX</t>
+          <t>Mid RCA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LCX</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>51.77940351438588</v>
+        <v>34.38341661144862</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moderate stenosis</t>
+          <t>Mild stenosis</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>268</v>
+        <v>1246</v>
       </c>
       <c r="I14" t="n">
-        <v>268</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Left coronary PDA</t>
+          <t>Proximal RCA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LCX</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49.06734541364825</v>
+        <v>15.82507038827767</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mild stenosis</t>
+          <t>Minimal stenosis</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>804</v>
+        <v>460</v>
       </c>
       <c r="I15" t="n">
-        <v>729</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mid RCA</t>
+          <t>Left Main</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40.16755430681539</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
+          <t>LCA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mild stenosis</t>
+          <t>Not assessable</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1246</v>
+        <v>363</v>
       </c>
       <c r="I16" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Proximal RCA</t>
+          <t>First diagonal (D1)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>16.76285285900079</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Minimal stenosis</t>
+          <t>Not assessable</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>460</v>
+        <v>71</v>
       </c>
       <c r="I17" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
